--- a/pklist/pklist_allmet_neg_1965.xlsx
+++ b/pklist/pklist_allmet_neg_1965.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxing\Documents\GitHub\autopeak\pklist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB1FEAD1-C235-41AB-AF1B-826D053A7DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D528A588-9709-4B84-A2AE-B10956B65B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1D23ACE-8DD7-4F10-8114-6E9B2AFE45C5}"/>
+    <workbookView xWindow="5850" yWindow="2625" windowWidth="19305" windowHeight="12270" xr2:uid="{D1D23ACE-8DD7-4F10-8114-6E9B2AFE45C5}"/>
   </bookViews>
   <sheets>
     <sheet name="all-met-1965" sheetId="1" r:id="rId1"/>
@@ -10638,6 +10638,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D31E354B-2982-44C8-912D-1C2F26E8378C}">
   <dimension ref="A1:E1966"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
